--- a/tools/importer/reports/import-purpose-vision-values.report.xlsx
+++ b/tools/importer/reports/import-purpose-vision-values.report.xlsx
@@ -70,7 +70,7 @@
     <t>purpose-vision-values</t>
   </si>
   <si>
-    <t>2026-09-02T16:33:34.707Z</t>
+    <t>2026-09-02T19:52:10.305Z</t>
   </si>
   <si>
     <t>Purpose, Vision &amp; Values | Covista</t>
